--- a/utils/Backup_Checker/backup_config.xlsx
+++ b/utils/Backup_Checker/backup_config.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://phenomenetworks-my.sharepoint.com/personal/itay-b_phenomenetworks_onmicrosoft_com/Documents/Laptop_Documents/GitHub/scripts/utils/Backup_Checker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{06BF08A4-A50F-4ED7-A0FC-6A974502048A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8964802-ECD7-40F6-B017-EF3CFC0E6D8C}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="8_{06BF08A4-A50F-4ED7-A0FC-6A974502048A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D637C613-07E2-4246-AFE2-025605F13B40}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Instructions" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Backup Config'!$A$2:$F$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Backup Config'!$A$2:$F$39</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="124">
   <si>
     <t>Phenome Networks — RDS Backup S3 Configuration</t>
   </si>
@@ -183,15 +183,6 @@
     <t>phenome-origene-mysql-backup</t>
   </si>
   <si>
-    <t>British American (BAT)</t>
-  </si>
-  <si>
-    <t>BAT</t>
-  </si>
-  <si>
-    <t>phenome-bat-mysql-weekly-backup</t>
-  </si>
-  <si>
     <t>East West Seeds Indonesia</t>
   </si>
   <si>
@@ -333,12 +324,6 @@
     <t>gdmseeds-dev-db-backup</t>
   </si>
   <si>
-    <t>Becks Hybrids</t>
-  </si>
-  <si>
-    <t>phenome-beckshybrids-mysql-backup</t>
-  </si>
-  <si>
     <t>Harnesstom</t>
   </si>
   <si>
@@ -412,13 +397,28 @@
   </si>
   <si>
     <t>enza-test-database-backup</t>
+  </si>
+  <si>
+    <t>phen-basf-prod-backup-mysql-weekly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">basf-dev-database-backup </t>
+  </si>
+  <si>
+    <t>weekly_backup/</t>
+  </si>
+  <si>
+    <t>basf-qual-backup-mysql-weekly</t>
+  </si>
+  <si>
+    <t>basf-mig-database-backup</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -540,6 +540,19 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF0F141A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -607,7 +620,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -670,6 +683,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -939,7 +957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5703125" customWidth="1"/>
@@ -1001,7 +1019,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="5" t="str">
-        <f t="shared" ref="F3:F44" si="0">IF(AND(D3&lt;&gt;"",E3&lt;&gt;""),"s3://"&amp;D3&amp;"/"&amp;E3&amp;"/","")</f>
+        <f t="shared" ref="F3:F42" si="0">IF(AND(D3&lt;&gt;"",E3&lt;&gt;""),"s3://"&amp;D3&amp;"/"&amp;E3&amp;"/","")</f>
         <v>s3://phn-p2g.prod-rds-backup/rds_weekly_backup/</v>
       </c>
       <c r="G3" s="6" t="s">
@@ -1369,512 +1387,528 @@
       </c>
     </row>
     <row r="19" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
-        <v>17</v>
-      </c>
-      <c r="B19" s="4" t="s">
+      <c r="A19" s="7">
+        <v>18</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>s3://ews-indonesia-mysql-daily-backups/rds_weekly_backup/</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="C20" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>s3://phenome-ramiro-mysql-weekly/weekly_backup/</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7">
+        <v>20</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>s3://phenome-mccain-mysql-weekly/rds_weekly_backup/</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>s3://phenome-bat-mysql-weekly-backup/weekly_backups/</v>
-      </c>
-      <c r="G19" s="6" t="s">
+      <c r="F22" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>s3://phenome-seedworks-mysql-backup/weekly_backups/</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="7">
+        <v>22</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>s3://phenome-ball-mysql-backup/rds_weekly_backup/</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F24" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>s3://phenome-onprem-mysql-backup/axia/</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="7">
+        <v>24</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F25" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>s3://phenome-gatesagonetest-mysql-weekly-backup/weekly_backups/</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>s3://phenome-gatesagone-weekly/weekly_backup/</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7">
+        <v>26</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>s3://phenome-fito-mysql-weekly/weekly_backup/</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>s3://phenome-solynta-mysql-weekly/weekly_backup/</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
+        <v>28</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F29" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>s3://phenome-testsolynta-rds-backup/weekly_backups/</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>s3://phenome-syngenta-mysql-weekly/weekly_backup/</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="7">
+        <v>30</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>s3://phenome-saproduceuk-rds-backup/rds_weekly_backup/</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
+        <v>31</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D32" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>s3://phen-basf-prod-backup-mysql-weekly/weekly_backup/</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="7">
+        <v>32</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="E33" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="F33" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>s3://basf-qual-backup-mysql-weekly/weekly_backup//</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3">
+        <v>33</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E34" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="F34" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>s3://basf-dev-database-backup /weekly_backup//</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="7">
+        <v>34</v>
+      </c>
+      <c r="B35" s="8" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
-        <v>18</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="E20" s="7" t="s">
+      <c r="C35" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D35" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="E35" t="s">
+        <v>121</v>
+      </c>
+      <c r="F35" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>s3://basf-mig-database-backup/weekly_backup//</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
+        <v>35</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F36" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>s3://phenome-onprem-mysql-backup/gdmseeds-prod-db-backup/</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="7">
+        <v>36</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="E37" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>s3://ews-indonesia-mysql-daily-backups/rds_weekly_backup/</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
-        <v>19</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E21" s="3" t="s">
+      <c r="F37" s="9" t="str">
+        <f>IF(AND(D37&lt;&gt;"",E37&lt;&gt;""),"s3://"&amp;D37&amp;"/"&amp;E37&amp;"/","")</f>
+        <v>s3://enza-test-database-backup/rds_weekly_backup/</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
+        <v>37</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>s3://enza-accept-database-backup/rds_weekly_backup/</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="7">
+        <v>38</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E39" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F21" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>s3://phenome-ramiro-mysql-weekly/weekly_backup/</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
-        <v>20</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E22" s="7" t="s">
+      <c r="F39" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>s3://enza-prod-weekly-database-backup/weekly_backup/</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
+        <v>39</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F22" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>s3://phenome-mccain-mysql-weekly/rds_weekly_backup/</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
-        <v>21</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F23" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>s3://phenome-seedworks-mysql-backup/weekly_backups/</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
-        <v>22</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>s3://phenome-ball-mysql-backup/rds_weekly_backup/</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
-        <v>23</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F25" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>s3://phenome-onprem-mysql-backup/axia/</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
-        <v>24</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F26" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>s3://phenome-gatesagonetest-mysql-weekly-backup/weekly_backups/</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
-        <v>25</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>s3://phenome-gatesagone-weekly/weekly_backup/</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="7">
-        <v>26</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>s3://phenome-fito-mysql-weekly/weekly_backup/</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="3">
-        <v>27</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>s3://phenome-solynta-mysql-weekly/weekly_backup/</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="7">
-        <v>28</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F30" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>s3://phenome-testsolynta-rds-backup/weekly_backups/</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3">
-        <v>29</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F31" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>s3://phenome-syngenta-mysql-weekly/weekly_backup/</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="7">
-        <v>30</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>s3://phenome-saproduceuk-rds-backup/rds_weekly_backup/</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="3">
-        <v>31</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="7">
-        <v>32</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3">
-        <v>33</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="7">
-        <v>34</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="3">
-        <v>35</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="F37" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>s3://phenome-onprem-mysql-backup/gdmseeds-prod-db-backup/</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="7">
-        <v>36</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="E38" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" s="9" t="str">
-        <f>IF(AND(D38&lt;&gt;"",E38&lt;&gt;""),"s3://"&amp;D38&amp;"/"&amp;E38&amp;"/","")</f>
-        <v>s3://enza-test-database-backup/rds_weekly_backup/</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="3">
-        <v>37</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F39" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>s3://enza-accept-database-backup/rds_weekly_backup/</v>
-      </c>
-      <c r="G39" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="7">
-        <v>38</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F40" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>s3://enza-prod-weekly-database-backup/weekly_backup/</v>
+      <c r="F40" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>s3://phenome-harmoniz-mysql-backup/rds_weekly_backup/</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>12</v>
@@ -1882,23 +1916,23 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E41" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="F41" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>s3://phenome-harmoniz-mysql-backup/rds_weekly_backup/</v>
+        <v>s3://phenome-onprem-mysql-backup/gdmseeds-dev-db-backup/</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>12</v>
@@ -1906,83 +1940,35 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B42" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="E42" s="3" t="s">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="F42" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>s3://phenome-onprem-mysql-backup/gdmseeds-dev-db-backup/</v>
+        <v>s3://phenome-harnesstom-mysql-backup/weekly_backup/</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="3">
-        <v>41</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F43" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>s3://phenome-beckshybrids-mysql-backup/weekly_backup/</v>
-      </c>
-      <c r="G43" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="3">
-        <v>42</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F44" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>s3://phenome-harnesstom-mysql-backup/weekly_backup/</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:F40" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:F39" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" showErrorMessage="1" errorTitle="Invalid value" error="Please select &quot;Yes&quot; or &quot;No&quot;" sqref="G3:G44" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="Invalid value" error="Please select &quot;Yes&quot; or &quot;No&quot;" sqref="G3:G42" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2005,7 +1991,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2013,37 +1999,37 @@
     </row>
     <row r="3" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2051,17 +2037,17 @@
     </row>
     <row r="11" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2069,27 +2055,27 @@
     </row>
     <row r="15" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2097,27 +2083,27 @@
     </row>
     <row r="21" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
